--- a/DOSSIES_MULTIFORMATO/SES_SUSAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SES_SUSAM/dossie.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14748048.9572181</t>
+          <t>4783356.52</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>43921619.17034938</t>
+          <t>8135935.19</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2028-09-30</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SES_SUSAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SES_SUSAM/dossie.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8135935.19</t>
+          <t>8230061.40</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2028-09-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
